--- a/output/pdf_financials_xlsx/BWR.xlsx
+++ b/output/pdf_financials_xlsx/BWR.xlsx
@@ -4623,40 +4623,40 @@
         </is>
       </c>
       <c r="B92" s="3" t="n">
-        <v>0</v>
+        <v>0.556127</v>
       </c>
       <c r="C92" s="3" t="n">
-        <v>0</v>
+        <v>0.6781430000000001</v>
       </c>
       <c r="D92" s="3" t="n">
-        <v>0</v>
+        <v>0.208369</v>
       </c>
       <c r="E92" s="3" t="n">
-        <v>0</v>
+        <v>0.355374</v>
       </c>
       <c r="F92" s="3" t="n">
-        <v>0</v>
+        <v>0.826483</v>
       </c>
       <c r="G92" s="3" t="n">
-        <v>0</v>
+        <v>0.8153319999999999</v>
       </c>
       <c r="H92" s="3" t="n">
-        <v>0</v>
+        <v>0.497242</v>
       </c>
       <c r="I92" s="3" t="n">
-        <v>0</v>
+        <v>0.677674</v>
       </c>
       <c r="J92" s="3" t="n">
-        <v>0</v>
+        <v>0.649544</v>
       </c>
       <c r="K92" s="3" t="n">
-        <v>0</v>
+        <v>0.606494</v>
       </c>
       <c r="L92" s="3" t="n">
-        <v>0</v>
+        <v>0.463128</v>
       </c>
       <c r="M92" s="3" t="n">
-        <v>0</v>
+        <v>0.455922</v>
       </c>
     </row>
     <row r="93">
@@ -7414,7 +7414,11 @@
           <t>Reserves (notes 7 and 8)</t>
         </is>
       </c>
-      <c r="D13" t="inlineStr"/>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E13" t="inlineStr">
         <is>
           <t>-</t>
@@ -8262,7 +8266,11 @@
           <t>Reserves (notes 8 and 9)</t>
         </is>
       </c>
-      <c r="D25" t="inlineStr"/>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E25" t="inlineStr">
         <is>
           <t>-</t>
@@ -8702,7 +8710,11 @@
           <t>Reserves (notes 8 and 9)</t>
         </is>
       </c>
-      <c r="D31" t="inlineStr"/>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E31" t="inlineStr">
         <is>
           <t>-</t>
@@ -9160,7 +9172,11 @@
           <t>Reserves (notes 8 and 9)</t>
         </is>
       </c>
-      <c r="D37" t="inlineStr"/>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E37" s="5" t="n">
         <v>0.556127</v>
       </c>

--- a/output/pdf_financials_xlsx/BWR.xlsx
+++ b/output/pdf_financials_xlsx/BWR.xlsx
@@ -895,13 +895,13 @@
         </is>
       </c>
       <c r="B12" s="3" t="n">
-        <v>0</v>
+        <v>0.001095</v>
       </c>
       <c r="C12" s="3" t="n">
-        <v>0</v>
+        <v>0.000752</v>
       </c>
       <c r="D12" s="3" t="n">
-        <v>0</v>
+        <v>-0.304582</v>
       </c>
       <c r="E12" s="1" t="inlineStr">
         <is>
@@ -1678,13 +1678,13 @@
         </is>
       </c>
       <c r="B27" s="3" t="n">
-        <v>-0.834472</v>
+        <v>-0.8355669999999999</v>
       </c>
       <c r="C27" s="3" t="n">
-        <v>-0.43293</v>
+        <v>-0.433682</v>
       </c>
       <c r="D27" s="3" t="n">
-        <v>-0.304582</v>
+        <v>0</v>
       </c>
       <c r="E27" s="1" t="inlineStr">
         <is>
@@ -1768,13 +1768,13 @@
         </is>
       </c>
       <c r="B29" s="3" t="n">
-        <v>-0.834472</v>
+        <v>-0.8355669999999999</v>
       </c>
       <c r="C29" s="3" t="n">
-        <v>-0.43293</v>
+        <v>-0.433682</v>
       </c>
       <c r="D29" s="3" t="n">
-        <v>-0.304582</v>
+        <v>0</v>
       </c>
       <c r="E29" s="1" t="inlineStr">
         <is>
@@ -1999,40 +1999,40 @@
         </is>
       </c>
       <c r="B34" s="3" t="n">
-        <v>0</v>
+        <v>0.054511</v>
       </c>
       <c r="C34" s="3" t="n">
-        <v>0</v>
+        <v>0.025613</v>
       </c>
       <c r="D34" s="3" t="n">
-        <v>0</v>
+        <v>0.014682</v>
       </c>
       <c r="E34" s="3" t="n">
-        <v>0</v>
+        <v>0.09689</v>
       </c>
       <c r="F34" s="3" t="n">
-        <v>0</v>
+        <v>0.06076</v>
       </c>
       <c r="G34" s="3" t="n">
-        <v>0</v>
+        <v>0.093094</v>
       </c>
       <c r="H34" s="3" t="n">
-        <v>0</v>
+        <v>0.138094</v>
       </c>
       <c r="I34" s="3" t="n">
-        <v>0</v>
+        <v>0.29237</v>
       </c>
       <c r="J34" s="3" t="n">
-        <v>0</v>
+        <v>0.109189</v>
       </c>
       <c r="K34" s="3" t="n">
-        <v>0</v>
+        <v>0.06489399999999999</v>
       </c>
       <c r="L34" s="3" t="n">
-        <v>0</v>
+        <v>0.006638</v>
       </c>
       <c r="M34" s="3" t="n">
-        <v>0</v>
+        <v>0.001583</v>
       </c>
     </row>
     <row r="35">
@@ -2085,40 +2085,40 @@
         </is>
       </c>
       <c r="B36" s="3" t="n">
-        <v>0.176095</v>
+        <v>0.230606</v>
       </c>
       <c r="C36" s="3" t="n">
-        <v>0</v>
+        <v>0.025613</v>
       </c>
       <c r="D36" s="3" t="n">
-        <v>0</v>
+        <v>0.014682</v>
       </c>
       <c r="E36" s="3" t="n">
-        <v>0</v>
+        <v>0.09689</v>
       </c>
       <c r="F36" s="3" t="n">
-        <v>0</v>
+        <v>0.06076</v>
       </c>
       <c r="G36" s="3" t="n">
-        <v>0</v>
+        <v>0.093094</v>
       </c>
       <c r="H36" s="3" t="n">
-        <v>0</v>
+        <v>0.138094</v>
       </c>
       <c r="I36" s="3" t="n">
-        <v>0</v>
+        <v>0.29237</v>
       </c>
       <c r="J36" s="3" t="n">
-        <v>0</v>
+        <v>0.109189</v>
       </c>
       <c r="K36" s="3" t="n">
-        <v>0</v>
+        <v>0.06489399999999999</v>
       </c>
       <c r="L36" s="3" t="n">
-        <v>0</v>
+        <v>0.006638</v>
       </c>
       <c r="M36" s="3" t="n">
-        <v>0</v>
+        <v>0.001583</v>
       </c>
     </row>
     <row r="37">
@@ -6624,7 +6624,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -8054,7 +8054,7 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E22" s="5" t="n">
@@ -18438,7 +18438,7 @@
       </c>
       <c r="D163" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E163" s="5" t="n">
@@ -18588,7 +18588,7 @@
       </c>
       <c r="D165" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E165" s="5" t="n">

--- a/output/pdf_financials_xlsx/BWR.xlsx
+++ b/output/pdf_financials_xlsx/BWR.xlsx
@@ -1075,10 +1075,10 @@
         </is>
       </c>
       <c r="B16" s="3" t="n">
-        <v>-0.834472</v>
+        <v>-0.740837</v>
       </c>
       <c r="C16" s="3" t="n">
-        <v>-0.43293</v>
+        <v>-0.376626</v>
       </c>
       <c r="D16" s="3" t="n">
         <v>-0.304582</v>
@@ -1120,10 +1120,10 @@
         </is>
       </c>
       <c r="B17" s="3" t="n">
-        <v>-0</v>
+        <v>-0.093635</v>
       </c>
       <c r="C17" s="3" t="n">
-        <v>-0</v>
+        <v>-0.056304</v>
       </c>
       <c r="D17" s="3" t="n">
         <v>-0</v>
@@ -1678,10 +1678,10 @@
         </is>
       </c>
       <c r="B27" s="3" t="n">
-        <v>-0.8355669999999999</v>
+        <v>-0.741932</v>
       </c>
       <c r="C27" s="3" t="n">
-        <v>-0.433682</v>
+        <v>-0.377378</v>
       </c>
       <c r="D27" s="3" t="n">
         <v>0</v>
@@ -1768,10 +1768,10 @@
         </is>
       </c>
       <c r="B29" s="3" t="n">
-        <v>-0.8355669999999999</v>
+        <v>-0.741932</v>
       </c>
       <c r="C29" s="3" t="n">
-        <v>-0.433682</v>
+        <v>-0.377378</v>
       </c>
       <c r="D29" s="3" t="n">
         <v>0</v>
@@ -1880,10 +1880,10 @@
         </is>
       </c>
       <c r="B31" s="3" t="n">
-        <v>-0</v>
+        <v>-12.63908255122247</v>
       </c>
       <c r="C31" s="3" t="n">
-        <v>-0</v>
+        <v>-14.94957862707301</v>
       </c>
       <c r="D31" s="3" t="n">
         <v>-0</v>
@@ -15954,7 +15954,11 @@
           <t>Deferred income tax recovery</t>
         </is>
       </c>
-      <c r="D129" t="inlineStr"/>
+      <c r="D129" t="inlineStr">
+        <is>
+          <t>DeferredTax</t>
+        </is>
+      </c>
       <c r="E129" s="5" t="n">
         <v>-0.093635</v>
       </c>
@@ -18512,7 +18516,11 @@
           <t>Deferred income tax recovery (note 14)</t>
         </is>
       </c>
-      <c r="D164" t="inlineStr"/>
+      <c r="D164" t="inlineStr">
+        <is>
+          <t>TaxProvision</t>
+        </is>
+      </c>
       <c r="E164" s="5" t="n">
         <v>0.093635</v>
       </c>
